--- a/Templates/template_productos.xlsx
+++ b/Templates/template_productos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,11 @@
           <t>DESCRIPCION</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FORMATO_MINIMO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -448,8 +453,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Producto de ejemplo 1</t>
-        </is>
+          <t>Aceite en bidones de 20L</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -460,9 +468,10 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Producto de ejemplo 2</t>
-        </is>
-      </c>
+          <t>Harina sin formato especial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -472,8 +481,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Producto de ejemplo 3</t>
-        </is>
+          <t>Cemento en sacos de 25kg</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
